--- a/scenarios/scenarios_aim1/aim1_results_tables.xlsx
+++ b/scenarios/scenarios_aim1/aim1_results_tables.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">Table 1. Cumulative deaths averted (2025-2050) by intervention scenario.</t>
   </si>
@@ -29,13 +29,40 @@
     <t xml:space="preserve">Average per year (thousands)</t>
   </si>
   <si>
+    <t xml:space="preserve">61.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,455.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,136.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,959.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Improved Hypertension Control</t>
   </si>
   <si>
-    <t xml:space="preserve">71.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,842.1</t>
+    <t xml:space="preserve">20.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improved Statin Uptake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">850.5</t>
   </si>
   <si>
     <t xml:space="preserve">Table 2. Deaths averted (millions) by intervention and cause of death.</t>
@@ -56,16 +83,25 @@
     <t xml:space="preserve">Ischemic stroke</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44</t>
+    <t xml:space="preserve">0.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46</t>
   </si>
   <si>
     <t xml:space="preserve">Table 3. Deaths averted by age group and intervention.</t>
@@ -92,73 +128,118 @@
     <t xml:space="preserve">&lt;70</t>
   </si>
   <si>
-    <t xml:space="preserve">227,826,554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">247,214,073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19,387,519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775,501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8%</t>
+    <t xml:space="preserve">167,028,201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175,228,222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,200,022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328,001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168,914,734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,313,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252,540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6%</t>
   </si>
   <si>
     <t xml:space="preserve">70-79</t>
   </si>
   <si>
-    <t xml:space="preserve">273,810,907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291,467,333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17,656,426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706,257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1%</t>
+    <t xml:space="preserve">176,788,396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180,543,266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,754,870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150,195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174,222,070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,321,196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252,848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5%</t>
   </si>
   <si>
     <t xml:space="preserve">80-89</t>
   </si>
   <si>
-    <t xml:space="preserve">385,540,942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413,222,379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27,681,437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,107,257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7%</t>
+    <t xml:space="preserve">235,085,787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,126,243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,040,455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281,618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235,086,128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,040,115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281,605</t>
   </si>
   <si>
     <t xml:space="preserve">90+</t>
   </si>
   <si>
-    <t xml:space="preserve">159,771,898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166,099,752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,327,853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253,114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8%</t>
+    <t xml:space="preserve">96,623,090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98,308,065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,684,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96,719,479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,588,586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Table 4. Country-level deaths averted (All Interventions, 2025-2050).</t>
@@ -542,14 +623,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4"/>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5" t="s">
         <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -572,41 +691,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -631,122 +767,214 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -771,30 +999,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/scenarios_aim1/aim1_results_tables.xlsx
+++ b/scenarios/scenarios_aim1/aim1_results_tables.xlsx
@@ -10,12 +10,13 @@
     <sheet name="T2_Deaths_by_Cause" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="T3_Deaths_by_Age" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="T4_Deaths_by_Country" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="T5_Deaths_by_Region" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="1215">
   <si>
     <t xml:space="preserve">Table 1. Cumulative deaths averted (2025-2050) by intervention scenario.</t>
   </si>
@@ -23,22 +24,55 @@
     <t xml:space="preserve">Intervention</t>
   </si>
   <si>
-    <t xml:space="preserve">Deaths averted (2025–2050, millions)</t>
+    <t xml:space="preserve">WHO Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths averted (M, 2025–2050)</t>
   </si>
   <si>
     <t xml:space="preserve">Average per year (thousands)</t>
   </si>
   <si>
+    <t xml:space="preserve">HTN Control (General)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target 1: 150M more with HTN controlled by 2030 (50% control)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTN Control (Diabetes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target 3: 80% BP control in people with diabetes by 2030</t>
+  </si>
+  <si>
     <t xml:space="preserve">61.38</t>
   </si>
   <si>
     <t xml:space="preserve">2,455.1</t>
   </si>
   <si>
-    <t xml:space="preserve">78.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,136.3</t>
+    <t xml:space="preserve">Improved Statin Uptake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target 2: &gt;=50% eligible adults on lipid-lowering therapy by 2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">850.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Interventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All WHO targets (1+2+3) combined</t>
   </si>
   <si>
     <t xml:space="preserve">99.00</t>
@@ -47,24 +81,6 @@
     <t xml:space="preserve">3,959.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Improved Hypertension Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improved Statin Uptake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">850.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Table 2. Deaths averted (millions) by intervention and cause of death.</t>
   </si>
   <si>
@@ -95,6 +111,18 @@
     <t xml:space="preserve">1.93</t>
   </si>
   <si>
+    <t xml:space="preserve">5.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.67</t>
+  </si>
+  <si>
     <t xml:space="preserve">–</t>
   </si>
   <si>
@@ -104,6 +132,18 @@
     <t xml:space="preserve">1.46</t>
   </si>
   <si>
+    <t xml:space="preserve">6.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.92</t>
+  </si>
+  <si>
     <t xml:space="preserve">Table 3. Deaths averted by age group and intervention.</t>
   </si>
   <si>
@@ -143,6 +183,18 @@
     <t xml:space="preserve">4.7%</t>
   </si>
   <si>
+    <t xml:space="preserve">159,815,403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,412,819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">616,513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">168,914,734</t>
   </si>
   <si>
@@ -155,6 +207,18 @@
     <t xml:space="preserve">3.6%</t>
   </si>
   <si>
+    <t xml:space="preserve">147,440,300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,787,922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,111,517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9%</t>
+  </si>
+  <si>
     <t xml:space="preserve">70-79</t>
   </si>
   <si>
@@ -173,6 +237,18 @@
     <t xml:space="preserve">2.1%</t>
   </si>
   <si>
+    <t xml:space="preserve">164,192,451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,350,815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">654,033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1%</t>
+  </si>
+  <si>
     <t xml:space="preserve">174,222,070</t>
   </si>
   <si>
@@ -185,6 +261,18 @@
     <t xml:space="preserve">3.5%</t>
   </si>
   <si>
+    <t xml:space="preserve">154,969,435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,573,831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,022,953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2%</t>
+  </si>
+  <si>
     <t xml:space="preserve">80-89</t>
   </si>
   <si>
@@ -203,6 +291,18 @@
     <t xml:space="preserve">2.9%</t>
   </si>
   <si>
+    <t xml:space="preserve">218,499,793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,626,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">945,058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">235,086,128</t>
   </si>
   <si>
@@ -212,6 +312,18 @@
     <t xml:space="preserve">281,605</t>
   </si>
   <si>
+    <t xml:space="preserve">205,908,483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,217,760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,448,710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0%</t>
+  </si>
+  <si>
     <t xml:space="preserve">90+</t>
   </si>
   <si>
@@ -230,6 +342,18 @@
     <t xml:space="preserve">1.7%</t>
   </si>
   <si>
+    <t xml:space="preserve">92,321,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,987,005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">239,480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1%</t>
+  </si>
+  <si>
     <t xml:space="preserve">96,719,479</t>
   </si>
   <si>
@@ -242,6 +366,18 @@
     <t xml:space="preserve">1.6%</t>
   </si>
   <si>
+    <t xml:space="preserve">88,890,418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,417,647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376,706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6%</t>
+  </si>
+  <si>
     <t xml:space="preserve">Table 4. Country-level deaths averted (All Interventions, 2025-2050).</t>
   </si>
   <si>
@@ -249,6 +385,3282 @@
   </si>
   <si>
     <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,803,900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,394,642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,590,742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,036,334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,934,231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">897,897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethiopia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,166,150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,975,616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">809,466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,280,851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,013,095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">732,244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,801,340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,403,401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">602,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanzania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,860,869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,385,741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">524,872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,574,203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,916,579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342,376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,031,884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,331,639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299,755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madagascar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,103,690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,401,994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298,303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">907,393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,165,943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258,551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameroon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">857,485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,109,553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252,068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">857,834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,107,587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249,752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozambique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">687,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">906,622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219,561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uganda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">963,220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,171,252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208,032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">663,465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">868,559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205,094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">603,881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">802,181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198,301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526,804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690,680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163,876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553,250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715,023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161,773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">467,954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">621,654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153,700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555,625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706,778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151,153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malawi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">469,602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613,897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144,295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimbabwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402,390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523,329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120,940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">411,992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">522,853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rwanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441,641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552,477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">366,719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">465,169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burundi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337,814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93,636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burkina Faso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">333,857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417,598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83,741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Leone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265,661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347,149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Togo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291,645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">364,419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72,774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210,720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">273,365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62,645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203,047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264,315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61,268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central African Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135,422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183,381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47,959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauritania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148,344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188,045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guinea-Bissau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83,889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108,223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eritrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109,562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132,153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauritius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106,570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127,543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lesotho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namibia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80,941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101,241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74,713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94,398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58,891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76,540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equatorial Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63,370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80,599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botswana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51,658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66,825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eswatini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41,402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comoros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sao Tome and Principe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seychelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Americas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,404,882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,080,294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,675,412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,639,665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,089,033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,449,367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,870,499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,812,508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942,008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,990,660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,404,020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413,360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,942,071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,330,576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388,504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venezuela (Bolivarian Republic of)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,852,802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,147,539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294,737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">997,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,213,321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216,121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927,045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,065,325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138,280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominican Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">770,017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">908,038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138,020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guatemala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">692,674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824,136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131,462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,098,420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,222,684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124,264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">794,507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902,579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108,072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">741,567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">843,083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101,515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,921,358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,021,017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99,660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolivia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507,252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">580,770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73,518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honduras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530,422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600,974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70,552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339,148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407,802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68,655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicaragua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">411,575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46,575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Salvador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">374,952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207,700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">244,356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159,458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194,845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176,542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207,233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186,567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215,178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28,612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costa Rica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263,767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289,628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136,752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161,019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guyana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56,849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suriname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46,501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahamas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31,322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Lucia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern Mediterranean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,442,812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,608,991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,166,179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86,647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,820,955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,446,368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,625,413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65,017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iran (Islamic Republic of)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,506,502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,555,379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,048,877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41,955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,932,161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,662,742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">730,581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,911,272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,596,972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">685,699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iraq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,775,093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,381,775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">606,681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afghanistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,976,208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,492,584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">516,376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,357,010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,745,966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388,956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,541,684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,900,575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358,891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syrian Arab Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,875,698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,119,048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243,351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">751,211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">899,323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148,112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609,635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">745,520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135,884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Arab Emirates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499,275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">579,023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79,749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668,258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75,197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somalia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225,241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300,073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74,832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310,035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363,070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53,035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebanon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326,148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379,082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52,934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palestine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276,871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324,464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47,593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335,974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91,883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105,978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71,650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84,527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Djibouti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44,406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russian Federation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,181,297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,728,661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,547,365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141,895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,524,373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,916,899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,392,526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55,701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,491,264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,256,857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">765,593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,912,129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,663,379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">751,250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzbekistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,596,938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,291,141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694,203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,132,891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,659,366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526,475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,389,063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,851,178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462,114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,901,594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,361,579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">459,985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,271,832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,695,900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">424,068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,702,898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,068,822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365,925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,269,982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,595,829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325,846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,958,554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,238,031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279,477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belarus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,904,215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,157,747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253,531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azerbaijan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,549,063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,802,372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253,308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,462,474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,669,677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207,203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tajikistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">884,884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,062,353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177,469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,552,556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,723,985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171,429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">818,889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">988,810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169,921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkmenistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872,881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,023,824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150,942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,500,030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,649,411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149,381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,405,904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,548,426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,109,033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,247,505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138,473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695,816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817,746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121,930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyrgyzstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816,397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935,131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118,734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">596,791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709,210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112,419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Moldova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550,489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">655,143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104,654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750,407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">847,142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96,735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">566,937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">658,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91,551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355,420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446,220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90,800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527,643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">618,101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90,458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">748,422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">837,793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89,371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">623,360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705,975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82,616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399,705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480,486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80,781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744,811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824,590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79,779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">487,366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">562,254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74,888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">559,093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">626,544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">595,205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">662,371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237,054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57,346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334,813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385,195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Macedonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340,498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386,489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45,991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">248,844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292,012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">239,967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282,429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42,461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194,816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232,162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37,346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177,043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209,426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184,269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214,120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montenegro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88,333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103,335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93,324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104,313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45,985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South-East Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95,530,332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112,147,357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,617,024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">664,681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,567,699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,623,113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,055,414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bangladesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15,164,913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,679,676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,514,764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60,591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myanmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,361,132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,716,497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,355,366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic People's Republic of Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,617,749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,187,062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569,313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thailand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,930,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,464,547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534,347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri Lanka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,944,488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,351,941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407,453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nepal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,186,751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,454,243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267,492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timor-Leste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82,940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99,514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhutan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44,523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maldives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29,697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162,177,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189,191,511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,014,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,080,578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viet Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,009,777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,709,764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,699,987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,207,482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,620,004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,412,521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56,501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,919,131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,908,276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">989,145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,022,337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,472,951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450,614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,178,327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,359,782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181,455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambodia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,120,357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,283,792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163,435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papua New Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706,232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846,907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140,674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,610,953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,749,085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138,132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taiwan (Province of China)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,260,509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,395,289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134,780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lao People's Democratic Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">545,814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">644,609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98,795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mongolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">244,892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298,959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265,559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301,797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singapore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243,654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267,123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69,301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90,365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solomon Islands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60,680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75,171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanuatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brunei Darussalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micronesia (Federated States of)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiribati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marshall Islands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Samoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 5. Deaths averted by region (All Interventions, 2025-2050).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194,719,431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227,314,957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,595,526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,303,821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148,452,378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175,805,015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27,352,638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,094,106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103,653,053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117,208,116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,555,064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542,203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,099,917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48,749,898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,649,982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55,233,850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64,340,097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,106,247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">364,250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56,050,008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62,787,712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,737,704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269,508</t>
   </si>
 </sst>
 </file>
@@ -602,8 +4014,9 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="85.58" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="38.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="68.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="31.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="28.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,54 +4034,64 @@
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4"/>
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5"/>
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6"/>
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -691,58 +4114,92 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +4214,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="64.3625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="29.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
@@ -767,214 +4224,398 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" t="s">
-        <v>74</v>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +4630,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="82.04375" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="42.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
@@ -999,30 +4640,4564 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" t="s">
+        <v>194</v>
+      </c>
+      <c r="G15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G20" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F21" t="s">
+        <v>229</v>
+      </c>
+      <c r="G21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" t="s">
+        <v>239</v>
+      </c>
+      <c r="F23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" t="s">
+        <v>251</v>
+      </c>
+      <c r="F25" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C26" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E26" t="s">
+        <v>257</v>
+      </c>
+      <c r="F26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C27" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" t="s">
+        <v>268</v>
+      </c>
+      <c r="E28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" t="s">
+        <v>270</v>
+      </c>
+      <c r="G28" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" t="s">
+        <v>272</v>
+      </c>
+      <c r="D29" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" t="s">
+        <v>275</v>
+      </c>
+      <c r="G29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" t="s">
+        <v>281</v>
+      </c>
+      <c r="G30" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C31" t="s">
+        <v>283</v>
+      </c>
+      <c r="D31" t="s">
+        <v>284</v>
+      </c>
+      <c r="E31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F31" t="s">
+        <v>286</v>
+      </c>
+      <c r="G31" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" t="s">
+        <v>289</v>
+      </c>
+      <c r="E32" t="s">
+        <v>290</v>
+      </c>
+      <c r="F32" t="s">
+        <v>291</v>
+      </c>
+      <c r="G32" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E33" t="s">
+        <v>296</v>
+      </c>
+      <c r="F33" t="s">
+        <v>297</v>
+      </c>
+      <c r="G33" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C34" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" t="s">
+        <v>302</v>
+      </c>
+      <c r="F34" t="s">
+        <v>303</v>
+      </c>
+      <c r="G34" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" t="s">
+        <v>305</v>
+      </c>
+      <c r="C35" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" t="s">
+        <v>308</v>
+      </c>
+      <c r="F35" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>311</v>
+      </c>
+      <c r="C36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" t="s">
+        <v>314</v>
+      </c>
+      <c r="F36" t="s">
+        <v>315</v>
+      </c>
+      <c r="G36" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" t="s">
+        <v>319</v>
+      </c>
+      <c r="E37" t="s">
+        <v>320</v>
+      </c>
+      <c r="F37" t="s">
+        <v>321</v>
+      </c>
+      <c r="G37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" t="s">
+        <v>323</v>
+      </c>
+      <c r="D38" t="s">
+        <v>324</v>
+      </c>
+      <c r="E38" t="s">
+        <v>325</v>
+      </c>
+      <c r="F38" t="s">
+        <v>326</v>
+      </c>
+      <c r="G38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>328</v>
+      </c>
+      <c r="C39" t="s">
+        <v>329</v>
+      </c>
+      <c r="D39" t="s">
+        <v>330</v>
+      </c>
+      <c r="E39" t="s">
+        <v>331</v>
+      </c>
+      <c r="F39" t="s">
+        <v>332</v>
+      </c>
+      <c r="G39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" t="s">
+        <v>335</v>
+      </c>
+      <c r="D40" t="s">
+        <v>336</v>
+      </c>
+      <c r="E40" t="s">
+        <v>337</v>
+      </c>
+      <c r="F40" t="s">
+        <v>338</v>
+      </c>
+      <c r="G40" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
+        <v>339</v>
+      </c>
+      <c r="C41" t="s">
+        <v>340</v>
+      </c>
+      <c r="D41" t="s">
+        <v>341</v>
+      </c>
+      <c r="E41" t="s">
+        <v>342</v>
+      </c>
+      <c r="F41" t="s">
+        <v>343</v>
+      </c>
+      <c r="G41" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
+        <v>344</v>
+      </c>
+      <c r="C42" t="s">
+        <v>345</v>
+      </c>
+      <c r="D42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F42" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" t="s">
+        <v>350</v>
+      </c>
+      <c r="C43" t="s">
+        <v>351</v>
+      </c>
+      <c r="D43" t="s">
+        <v>352</v>
+      </c>
+      <c r="E43" t="s">
+        <v>353</v>
+      </c>
+      <c r="F43" t="s">
+        <v>354</v>
+      </c>
+      <c r="G43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" t="s">
+        <v>355</v>
+      </c>
+      <c r="C44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D44" t="s">
+        <v>357</v>
+      </c>
+      <c r="E44" t="s">
+        <v>358</v>
+      </c>
+      <c r="F44" t="s">
+        <v>359</v>
+      </c>
+      <c r="G44" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" t="s">
+        <v>360</v>
+      </c>
+      <c r="C45" t="s">
+        <v>361</v>
+      </c>
+      <c r="D45" t="s">
+        <v>362</v>
+      </c>
+      <c r="E45" t="s">
+        <v>363</v>
+      </c>
+      <c r="F45" t="s">
+        <v>364</v>
+      </c>
+      <c r="G45" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" t="s">
+        <v>365</v>
+      </c>
+      <c r="C46" t="s">
+        <v>366</v>
+      </c>
+      <c r="D46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E46" t="s">
+        <v>368</v>
+      </c>
+      <c r="F46" t="s">
+        <v>369</v>
+      </c>
+      <c r="G46" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" t="s">
+        <v>371</v>
+      </c>
+      <c r="C47" t="s">
+        <v>372</v>
+      </c>
+      <c r="D47" t="s">
+        <v>373</v>
+      </c>
+      <c r="E47" t="s">
+        <v>374</v>
+      </c>
+      <c r="F47" t="s">
+        <v>375</v>
+      </c>
+      <c r="G47" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" t="s">
+        <v>377</v>
+      </c>
+      <c r="C48" t="s">
+        <v>378</v>
+      </c>
+      <c r="D48" t="s">
+        <v>379</v>
+      </c>
+      <c r="E48" t="s">
+        <v>380</v>
+      </c>
+      <c r="F48" t="s">
+        <v>381</v>
+      </c>
+      <c r="G48" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" t="s">
+        <v>382</v>
+      </c>
+      <c r="C49" t="s">
+        <v>383</v>
+      </c>
+      <c r="D49" t="s">
+        <v>384</v>
+      </c>
+      <c r="E49" t="s">
+        <v>385</v>
+      </c>
+      <c r="F49" t="s">
+        <v>386</v>
+      </c>
+      <c r="G49" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s">
+        <v>387</v>
+      </c>
+      <c r="C50" t="s">
+        <v>388</v>
+      </c>
+      <c r="D50" t="s">
+        <v>389</v>
+      </c>
+      <c r="E50" t="s">
+        <v>390</v>
+      </c>
+      <c r="F50" t="s">
+        <v>391</v>
+      </c>
+      <c r="G50" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>393</v>
+      </c>
+      <c r="B51" t="s">
+        <v>394</v>
+      </c>
+      <c r="C51" t="s">
+        <v>395</v>
+      </c>
+      <c r="D51" t="s">
+        <v>396</v>
+      </c>
+      <c r="E51" t="s">
+        <v>397</v>
+      </c>
+      <c r="F51" t="s">
+        <v>398</v>
+      </c>
+      <c r="G51" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>393</v>
+      </c>
+      <c r="B52" t="s">
+        <v>400</v>
+      </c>
+      <c r="C52" t="s">
+        <v>401</v>
+      </c>
+      <c r="D52" t="s">
+        <v>402</v>
+      </c>
+      <c r="E52" t="s">
+        <v>403</v>
+      </c>
+      <c r="F52" t="s">
+        <v>404</v>
+      </c>
+      <c r="G52" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>393</v>
+      </c>
+      <c r="B53" t="s">
+        <v>406</v>
+      </c>
+      <c r="C53" t="s">
+        <v>407</v>
+      </c>
+      <c r="D53" t="s">
+        <v>408</v>
+      </c>
+      <c r="E53" t="s">
+        <v>409</v>
+      </c>
+      <c r="F53" t="s">
+        <v>410</v>
+      </c>
+      <c r="G53" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>393</v>
+      </c>
+      <c r="B54" t="s">
+        <v>412</v>
+      </c>
+      <c r="C54" t="s">
+        <v>413</v>
+      </c>
+      <c r="D54" t="s">
+        <v>414</v>
+      </c>
+      <c r="E54" t="s">
+        <v>415</v>
+      </c>
+      <c r="F54" t="s">
+        <v>416</v>
+      </c>
+      <c r="G54" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>393</v>
+      </c>
+      <c r="B55" t="s">
+        <v>418</v>
+      </c>
+      <c r="C55" t="s">
+        <v>419</v>
+      </c>
+      <c r="D55" t="s">
+        <v>420</v>
+      </c>
+      <c r="E55" t="s">
+        <v>421</v>
+      </c>
+      <c r="F55" t="s">
+        <v>422</v>
+      </c>
+      <c r="G55" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s">
+        <v>424</v>
+      </c>
+      <c r="C56" t="s">
+        <v>425</v>
+      </c>
+      <c r="D56" t="s">
+        <v>426</v>
+      </c>
+      <c r="E56" t="s">
+        <v>427</v>
+      </c>
+      <c r="F56" t="s">
+        <v>428</v>
+      </c>
+      <c r="G56" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>393</v>
+      </c>
+      <c r="B57" t="s">
+        <v>430</v>
+      </c>
+      <c r="C57" t="s">
+        <v>431</v>
+      </c>
+      <c r="D57" t="s">
+        <v>432</v>
+      </c>
+      <c r="E57" t="s">
+        <v>433</v>
+      </c>
+      <c r="F57" t="s">
+        <v>434</v>
+      </c>
+      <c r="G57" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>393</v>
+      </c>
+      <c r="B58" t="s">
+        <v>435</v>
+      </c>
+      <c r="C58" t="s">
+        <v>436</v>
+      </c>
+      <c r="D58" t="s">
+        <v>437</v>
+      </c>
+      <c r="E58" t="s">
+        <v>438</v>
+      </c>
+      <c r="F58" t="s">
+        <v>439</v>
+      </c>
+      <c r="G58" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>393</v>
+      </c>
+      <c r="B59" t="s">
+        <v>441</v>
+      </c>
+      <c r="C59" t="s">
+        <v>442</v>
+      </c>
+      <c r="D59" t="s">
+        <v>443</v>
+      </c>
+      <c r="E59" t="s">
+        <v>444</v>
+      </c>
+      <c r="F59" t="s">
+        <v>445</v>
+      </c>
+      <c r="G59" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>393</v>
+      </c>
+      <c r="B60" t="s">
+        <v>447</v>
+      </c>
+      <c r="C60" t="s">
+        <v>448</v>
+      </c>
+      <c r="D60" t="s">
+        <v>449</v>
+      </c>
+      <c r="E60" t="s">
+        <v>450</v>
+      </c>
+      <c r="F60" t="s">
+        <v>451</v>
+      </c>
+      <c r="G60" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>393</v>
+      </c>
+      <c r="B61" t="s">
+        <v>453</v>
+      </c>
+      <c r="C61" t="s">
+        <v>454</v>
+      </c>
+      <c r="D61" t="s">
+        <v>455</v>
+      </c>
+      <c r="E61" t="s">
+        <v>456</v>
+      </c>
+      <c r="F61" t="s">
+        <v>457</v>
+      </c>
+      <c r="G61" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>393</v>
+      </c>
+      <c r="B62" t="s">
+        <v>459</v>
+      </c>
+      <c r="C62" t="s">
+        <v>460</v>
+      </c>
+      <c r="D62" t="s">
+        <v>461</v>
+      </c>
+      <c r="E62" t="s">
+        <v>462</v>
+      </c>
+      <c r="F62" t="s">
+        <v>463</v>
+      </c>
+      <c r="G62" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>393</v>
+      </c>
+      <c r="B63" t="s">
+        <v>465</v>
+      </c>
+      <c r="C63" t="s">
+        <v>466</v>
+      </c>
+      <c r="D63" t="s">
+        <v>467</v>
+      </c>
+      <c r="E63" t="s">
+        <v>468</v>
+      </c>
+      <c r="F63" t="s">
+        <v>469</v>
+      </c>
+      <c r="G63" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>393</v>
+      </c>
+      <c r="B64" t="s">
+        <v>470</v>
+      </c>
+      <c r="C64" t="s">
+        <v>471</v>
+      </c>
+      <c r="D64" t="s">
+        <v>472</v>
+      </c>
+      <c r="E64" t="s">
+        <v>473</v>
+      </c>
+      <c r="F64" t="s">
+        <v>474</v>
+      </c>
+      <c r="G64" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s">
+        <v>476</v>
+      </c>
+      <c r="C65" t="s">
+        <v>477</v>
+      </c>
+      <c r="D65" t="s">
+        <v>478</v>
+      </c>
+      <c r="E65" t="s">
+        <v>479</v>
+      </c>
+      <c r="F65" t="s">
+        <v>480</v>
+      </c>
+      <c r="G65" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>393</v>
+      </c>
+      <c r="B66" t="s">
+        <v>482</v>
+      </c>
+      <c r="C66" t="s">
+        <v>483</v>
+      </c>
+      <c r="D66" t="s">
+        <v>484</v>
+      </c>
+      <c r="E66" t="s">
+        <v>485</v>
+      </c>
+      <c r="F66" t="s">
+        <v>486</v>
+      </c>
+      <c r="G66" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>393</v>
+      </c>
+      <c r="B67" t="s">
+        <v>488</v>
+      </c>
+      <c r="C67" t="s">
+        <v>489</v>
+      </c>
+      <c r="D67" t="s">
+        <v>490</v>
+      </c>
+      <c r="E67" t="s">
+        <v>491</v>
+      </c>
+      <c r="F67" t="s">
+        <v>492</v>
+      </c>
+      <c r="G67" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>393</v>
+      </c>
+      <c r="B68" t="s">
+        <v>494</v>
+      </c>
+      <c r="C68" t="s">
+        <v>495</v>
+      </c>
+      <c r="D68" t="s">
+        <v>496</v>
+      </c>
+      <c r="E68" t="s">
+        <v>497</v>
+      </c>
+      <c r="F68" t="s">
+        <v>498</v>
+      </c>
+      <c r="G68" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>393</v>
+      </c>
+      <c r="B69" t="s">
+        <v>500</v>
+      </c>
+      <c r="C69" t="s">
+        <v>501</v>
+      </c>
+      <c r="D69" t="s">
+        <v>502</v>
+      </c>
+      <c r="E69" t="s">
+        <v>503</v>
+      </c>
+      <c r="F69" t="s">
+        <v>504</v>
+      </c>
+      <c r="G69" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>393</v>
+      </c>
+      <c r="B70" t="s">
+        <v>506</v>
+      </c>
+      <c r="C70" t="s">
+        <v>507</v>
+      </c>
+      <c r="D70" t="s">
+        <v>508</v>
+      </c>
+      <c r="E70" t="s">
+        <v>509</v>
+      </c>
+      <c r="F70" t="s">
+        <v>510</v>
+      </c>
+      <c r="G70" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>393</v>
+      </c>
+      <c r="B71" t="s">
+        <v>511</v>
+      </c>
+      <c r="C71" t="s">
+        <v>512</v>
+      </c>
+      <c r="D71" t="s">
+        <v>513</v>
+      </c>
+      <c r="E71" t="s">
+        <v>514</v>
+      </c>
+      <c r="F71" t="s">
+        <v>515</v>
+      </c>
+      <c r="G71" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>393</v>
+      </c>
+      <c r="B72" t="s">
+        <v>517</v>
+      </c>
+      <c r="C72" t="s">
+        <v>518</v>
+      </c>
+      <c r="D72" t="s">
+        <v>519</v>
+      </c>
+      <c r="E72" t="s">
+        <v>520</v>
+      </c>
+      <c r="F72" t="s">
+        <v>521</v>
+      </c>
+      <c r="G72" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>393</v>
+      </c>
+      <c r="B73" t="s">
+        <v>523</v>
+      </c>
+      <c r="C73" t="s">
+        <v>524</v>
+      </c>
+      <c r="D73" t="s">
+        <v>525</v>
+      </c>
+      <c r="E73" t="s">
+        <v>526</v>
+      </c>
+      <c r="F73" t="s">
+        <v>527</v>
+      </c>
+      <c r="G73" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>393</v>
+      </c>
+      <c r="B74" t="s">
+        <v>529</v>
+      </c>
+      <c r="C74" t="s">
+        <v>530</v>
+      </c>
+      <c r="D74" t="s">
+        <v>531</v>
+      </c>
+      <c r="E74" t="s">
+        <v>532</v>
+      </c>
+      <c r="F74" t="s">
+        <v>533</v>
+      </c>
+      <c r="G74" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" t="s">
+        <v>535</v>
+      </c>
+      <c r="C75" t="s">
+        <v>536</v>
+      </c>
+      <c r="D75" t="s">
+        <v>537</v>
+      </c>
+      <c r="E75" t="s">
+        <v>538</v>
+      </c>
+      <c r="F75" t="s">
+        <v>539</v>
+      </c>
+      <c r="G75" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>393</v>
+      </c>
+      <c r="B76" t="s">
+        <v>541</v>
+      </c>
+      <c r="C76" t="s">
+        <v>542</v>
+      </c>
+      <c r="D76" t="s">
+        <v>543</v>
+      </c>
+      <c r="E76" t="s">
+        <v>544</v>
+      </c>
+      <c r="F76" t="s">
+        <v>545</v>
+      </c>
+      <c r="G76" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>393</v>
+      </c>
+      <c r="B77" t="s">
+        <v>547</v>
+      </c>
+      <c r="C77" t="s">
+        <v>548</v>
+      </c>
+      <c r="D77" t="s">
+        <v>549</v>
+      </c>
+      <c r="E77" t="s">
+        <v>550</v>
+      </c>
+      <c r="F77" t="s">
+        <v>551</v>
+      </c>
+      <c r="G77" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>393</v>
+      </c>
+      <c r="B78" t="s">
+        <v>553</v>
+      </c>
+      <c r="C78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D78" t="s">
+        <v>555</v>
+      </c>
+      <c r="E78" t="s">
+        <v>556</v>
+      </c>
+      <c r="F78" t="s">
+        <v>557</v>
+      </c>
+      <c r="G78" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>393</v>
+      </c>
+      <c r="B79" t="s">
+        <v>558</v>
+      </c>
+      <c r="C79" t="s">
+        <v>559</v>
+      </c>
+      <c r="D79" t="s">
+        <v>560</v>
+      </c>
+      <c r="E79" t="s">
+        <v>561</v>
+      </c>
+      <c r="F79" t="s">
+        <v>562</v>
+      </c>
+      <c r="G79" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>393</v>
+      </c>
+      <c r="B80" t="s">
+        <v>564</v>
+      </c>
+      <c r="C80" t="s">
+        <v>565</v>
+      </c>
+      <c r="D80" t="s">
+        <v>566</v>
+      </c>
+      <c r="E80" t="s">
+        <v>480</v>
+      </c>
+      <c r="F80" t="s">
+        <v>567</v>
+      </c>
+      <c r="G80" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>393</v>
+      </c>
+      <c r="B81" t="s">
+        <v>568</v>
+      </c>
+      <c r="C81" t="s">
+        <v>569</v>
+      </c>
+      <c r="D81" t="s">
+        <v>570</v>
+      </c>
+      <c r="E81" t="s">
+        <v>571</v>
+      </c>
+      <c r="F81" t="s">
+        <v>572</v>
+      </c>
+      <c r="G81" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>393</v>
+      </c>
+      <c r="B82" t="s">
+        <v>574</v>
+      </c>
+      <c r="C82" t="s">
+        <v>575</v>
+      </c>
+      <c r="D82" t="s">
+        <v>576</v>
+      </c>
+      <c r="E82" t="s">
+        <v>577</v>
+      </c>
+      <c r="F82" t="s">
+        <v>578</v>
+      </c>
+      <c r="G82" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>393</v>
+      </c>
+      <c r="B83" t="s">
+        <v>580</v>
+      </c>
+      <c r="C83" t="s">
+        <v>581</v>
+      </c>
+      <c r="D83" t="s">
+        <v>582</v>
+      </c>
+      <c r="E83" t="s">
+        <v>583</v>
+      </c>
+      <c r="F83" t="s">
+        <v>584</v>
+      </c>
+      <c r="G83" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>393</v>
+      </c>
+      <c r="B84" t="s">
+        <v>586</v>
+      </c>
+      <c r="C84" t="s">
+        <v>587</v>
+      </c>
+      <c r="D84" t="s">
+        <v>588</v>
+      </c>
+      <c r="E84" t="s">
+        <v>589</v>
+      </c>
+      <c r="F84" t="s">
+        <v>590</v>
+      </c>
+      <c r="G84" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>393</v>
+      </c>
+      <c r="B85" t="s">
+        <v>592</v>
+      </c>
+      <c r="C85" t="s">
+        <v>593</v>
+      </c>
+      <c r="D85" t="s">
+        <v>594</v>
+      </c>
+      <c r="E85" t="s">
+        <v>595</v>
+      </c>
+      <c r="F85" t="s">
+        <v>590</v>
+      </c>
+      <c r="G85" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>596</v>
+      </c>
+      <c r="B86" t="s">
+        <v>597</v>
+      </c>
+      <c r="C86" t="s">
+        <v>598</v>
+      </c>
+      <c r="D86" t="s">
+        <v>599</v>
+      </c>
+      <c r="E86" t="s">
+        <v>600</v>
+      </c>
+      <c r="F86" t="s">
+        <v>601</v>
+      </c>
+      <c r="G86" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>596</v>
+      </c>
+      <c r="B87" t="s">
+        <v>603</v>
+      </c>
+      <c r="C87" t="s">
+        <v>604</v>
+      </c>
+      <c r="D87" t="s">
+        <v>605</v>
+      </c>
+      <c r="E87" t="s">
+        <v>606</v>
+      </c>
+      <c r="F87" t="s">
+        <v>607</v>
+      </c>
+      <c r="G87" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>596</v>
+      </c>
+      <c r="B88" t="s">
+        <v>608</v>
+      </c>
+      <c r="C88" t="s">
+        <v>609</v>
+      </c>
+      <c r="D88" t="s">
+        <v>610</v>
+      </c>
+      <c r="E88" t="s">
+        <v>611</v>
+      </c>
+      <c r="F88" t="s">
+        <v>612</v>
+      </c>
+      <c r="G88" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>596</v>
+      </c>
+      <c r="B89" t="s">
+        <v>614</v>
+      </c>
+      <c r="C89" t="s">
+        <v>615</v>
+      </c>
+      <c r="D89" t="s">
+        <v>616</v>
+      </c>
+      <c r="E89" t="s">
+        <v>617</v>
+      </c>
+      <c r="F89" t="s">
+        <v>618</v>
+      </c>
+      <c r="G89" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>596</v>
+      </c>
+      <c r="B90" t="s">
+        <v>620</v>
+      </c>
+      <c r="C90" t="s">
+        <v>621</v>
+      </c>
+      <c r="D90" t="s">
+        <v>622</v>
+      </c>
+      <c r="E90" t="s">
+        <v>623</v>
+      </c>
+      <c r="F90" t="s">
+        <v>624</v>
+      </c>
+      <c r="G90" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>596</v>
+      </c>
+      <c r="B91" t="s">
+        <v>626</v>
+      </c>
+      <c r="C91" t="s">
+        <v>627</v>
+      </c>
+      <c r="D91" t="s">
+        <v>628</v>
+      </c>
+      <c r="E91" t="s">
+        <v>629</v>
+      </c>
+      <c r="F91" t="s">
+        <v>630</v>
+      </c>
+      <c r="G91" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>596</v>
+      </c>
+      <c r="B92" t="s">
+        <v>631</v>
+      </c>
+      <c r="C92" t="s">
+        <v>632</v>
+      </c>
+      <c r="D92" t="s">
+        <v>633</v>
+      </c>
+      <c r="E92" t="s">
+        <v>634</v>
+      </c>
+      <c r="F92" t="s">
+        <v>635</v>
+      </c>
+      <c r="G92" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>596</v>
+      </c>
+      <c r="B93" t="s">
+        <v>636</v>
+      </c>
+      <c r="C93" t="s">
+        <v>637</v>
+      </c>
+      <c r="D93" t="s">
+        <v>638</v>
+      </c>
+      <c r="E93" t="s">
+        <v>639</v>
+      </c>
+      <c r="F93" t="s">
+        <v>640</v>
+      </c>
+      <c r="G93" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>596</v>
+      </c>
+      <c r="B94" t="s">
+        <v>641</v>
+      </c>
+      <c r="C94" t="s">
+        <v>642</v>
+      </c>
+      <c r="D94" t="s">
+        <v>643</v>
+      </c>
+      <c r="E94" t="s">
+        <v>644</v>
+      </c>
+      <c r="F94" t="s">
+        <v>645</v>
+      </c>
+      <c r="G94" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>596</v>
+      </c>
+      <c r="B95" t="s">
+        <v>647</v>
+      </c>
+      <c r="C95" t="s">
+        <v>648</v>
+      </c>
+      <c r="D95" t="s">
+        <v>649</v>
+      </c>
+      <c r="E95" t="s">
+        <v>650</v>
+      </c>
+      <c r="F95" t="s">
+        <v>651</v>
+      </c>
+      <c r="G95" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>596</v>
+      </c>
+      <c r="B96" t="s">
+        <v>653</v>
+      </c>
+      <c r="C96" t="s">
+        <v>654</v>
+      </c>
+      <c r="D96" t="s">
+        <v>655</v>
+      </c>
+      <c r="E96" t="s">
+        <v>656</v>
+      </c>
+      <c r="F96" t="s">
+        <v>657</v>
+      </c>
+      <c r="G96" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>596</v>
+      </c>
+      <c r="B97" t="s">
+        <v>658</v>
+      </c>
+      <c r="C97" t="s">
+        <v>659</v>
+      </c>
+      <c r="D97" t="s">
+        <v>660</v>
+      </c>
+      <c r="E97" t="s">
+        <v>661</v>
+      </c>
+      <c r="F97" t="s">
+        <v>662</v>
+      </c>
+      <c r="G97" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>596</v>
+      </c>
+      <c r="B98" t="s">
+        <v>663</v>
+      </c>
+      <c r="C98" t="s">
+        <v>664</v>
+      </c>
+      <c r="D98" t="s">
+        <v>665</v>
+      </c>
+      <c r="E98" t="s">
+        <v>666</v>
+      </c>
+      <c r="F98" t="s">
+        <v>667</v>
+      </c>
+      <c r="G98" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>596</v>
+      </c>
+      <c r="B99" t="s">
+        <v>668</v>
+      </c>
+      <c r="C99" t="s">
+        <v>669</v>
+      </c>
+      <c r="D99" t="s">
+        <v>670</v>
+      </c>
+      <c r="E99" t="s">
+        <v>671</v>
+      </c>
+      <c r="F99" t="s">
+        <v>672</v>
+      </c>
+      <c r="G99" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>596</v>
+      </c>
+      <c r="B100" t="s">
+        <v>673</v>
+      </c>
+      <c r="C100" t="s">
+        <v>674</v>
+      </c>
+      <c r="D100" t="s">
+        <v>675</v>
+      </c>
+      <c r="E100" t="s">
+        <v>676</v>
+      </c>
+      <c r="F100" t="s">
+        <v>677</v>
+      </c>
+      <c r="G100" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>596</v>
+      </c>
+      <c r="B101" t="s">
+        <v>679</v>
+      </c>
+      <c r="C101" t="s">
+        <v>680</v>
+      </c>
+      <c r="D101" t="s">
+        <v>681</v>
+      </c>
+      <c r="E101" t="s">
+        <v>682</v>
+      </c>
+      <c r="F101" t="s">
+        <v>683</v>
+      </c>
+      <c r="G101" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>596</v>
+      </c>
+      <c r="B102" t="s">
+        <v>684</v>
+      </c>
+      <c r="C102" t="s">
+        <v>685</v>
+      </c>
+      <c r="D102" t="s">
+        <v>686</v>
+      </c>
+      <c r="E102" t="s">
+        <v>687</v>
+      </c>
+      <c r="F102" t="s">
+        <v>688</v>
+      </c>
+      <c r="G102" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>596</v>
+      </c>
+      <c r="B103" t="s">
+        <v>690</v>
+      </c>
+      <c r="C103" t="s">
+        <v>691</v>
+      </c>
+      <c r="D103" t="s">
+        <v>692</v>
+      </c>
+      <c r="E103" t="s">
+        <v>693</v>
+      </c>
+      <c r="F103" t="s">
+        <v>694</v>
+      </c>
+      <c r="G103" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>596</v>
+      </c>
+      <c r="B104" t="s">
+        <v>696</v>
+      </c>
+      <c r="C104" t="s">
+        <v>697</v>
+      </c>
+      <c r="D104" t="s">
+        <v>698</v>
+      </c>
+      <c r="E104" t="s">
+        <v>699</v>
+      </c>
+      <c r="F104" t="s">
+        <v>700</v>
+      </c>
+      <c r="G104" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>596</v>
+      </c>
+      <c r="B105" t="s">
+        <v>702</v>
+      </c>
+      <c r="C105" t="s">
+        <v>703</v>
+      </c>
+      <c r="D105" t="s">
+        <v>704</v>
+      </c>
+      <c r="E105" t="s">
+        <v>705</v>
+      </c>
+      <c r="F105" t="s">
+        <v>706</v>
+      </c>
+      <c r="G105" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>596</v>
+      </c>
+      <c r="B106" t="s">
+        <v>707</v>
+      </c>
+      <c r="C106" t="s">
+        <v>708</v>
+      </c>
+      <c r="D106" t="s">
+        <v>709</v>
+      </c>
+      <c r="E106" t="s">
+        <v>710</v>
+      </c>
+      <c r="F106" t="s">
+        <v>711</v>
+      </c>
+      <c r="G106" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>596</v>
+      </c>
+      <c r="B107" t="s">
+        <v>712</v>
+      </c>
+      <c r="C107" t="s">
+        <v>713</v>
+      </c>
+      <c r="D107" t="s">
+        <v>714</v>
+      </c>
+      <c r="E107" t="s">
+        <v>715</v>
+      </c>
+      <c r="F107" t="s">
+        <v>716</v>
+      </c>
+      <c r="G107" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>717</v>
+      </c>
+      <c r="B108" t="s">
+        <v>718</v>
+      </c>
+      <c r="C108" t="s">
+        <v>719</v>
+      </c>
+      <c r="D108" t="s">
+        <v>720</v>
+      </c>
+      <c r="E108" t="s">
+        <v>721</v>
+      </c>
+      <c r="F108" t="s">
+        <v>722</v>
+      </c>
+      <c r="G108" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>717</v>
+      </c>
+      <c r="B109" t="s">
+        <v>723</v>
+      </c>
+      <c r="C109" t="s">
+        <v>724</v>
+      </c>
+      <c r="D109" t="s">
+        <v>725</v>
+      </c>
+      <c r="E109" t="s">
+        <v>726</v>
+      </c>
+      <c r="F109" t="s">
+        <v>727</v>
+      </c>
+      <c r="G109" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>717</v>
+      </c>
+      <c r="B110" t="s">
+        <v>728</v>
+      </c>
+      <c r="C110" t="s">
+        <v>729</v>
+      </c>
+      <c r="D110" t="s">
+        <v>730</v>
+      </c>
+      <c r="E110" t="s">
+        <v>731</v>
+      </c>
+      <c r="F110" t="s">
+        <v>732</v>
+      </c>
+      <c r="G110" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>717</v>
+      </c>
+      <c r="B111" t="s">
+        <v>734</v>
+      </c>
+      <c r="C111" t="s">
+        <v>735</v>
+      </c>
+      <c r="D111" t="s">
+        <v>736</v>
+      </c>
+      <c r="E111" t="s">
+        <v>737</v>
+      </c>
+      <c r="F111" t="s">
+        <v>738</v>
+      </c>
+      <c r="G111" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>717</v>
+      </c>
+      <c r="B112" t="s">
+        <v>739</v>
+      </c>
+      <c r="C112" t="s">
+        <v>740</v>
+      </c>
+      <c r="D112" t="s">
+        <v>741</v>
+      </c>
+      <c r="E112" t="s">
+        <v>742</v>
+      </c>
+      <c r="F112" t="s">
+        <v>743</v>
+      </c>
+      <c r="G112" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>717</v>
+      </c>
+      <c r="B113" t="s">
+        <v>744</v>
+      </c>
+      <c r="C113" t="s">
+        <v>745</v>
+      </c>
+      <c r="D113" t="s">
+        <v>746</v>
+      </c>
+      <c r="E113" t="s">
+        <v>747</v>
+      </c>
+      <c r="F113" t="s">
+        <v>748</v>
+      </c>
+      <c r="G113" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>717</v>
+      </c>
+      <c r="B114" t="s">
+        <v>749</v>
+      </c>
+      <c r="C114" t="s">
+        <v>750</v>
+      </c>
+      <c r="D114" t="s">
+        <v>751</v>
+      </c>
+      <c r="E114" t="s">
+        <v>752</v>
+      </c>
+      <c r="F114" t="s">
+        <v>753</v>
+      </c>
+      <c r="G114" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>717</v>
+      </c>
+      <c r="B115" t="s">
+        <v>755</v>
+      </c>
+      <c r="C115" t="s">
+        <v>756</v>
+      </c>
+      <c r="D115" t="s">
+        <v>757</v>
+      </c>
+      <c r="E115" t="s">
+        <v>758</v>
+      </c>
+      <c r="F115" t="s">
+        <v>759</v>
+      </c>
+      <c r="G115" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>717</v>
+      </c>
+      <c r="B116" t="s">
+        <v>761</v>
+      </c>
+      <c r="C116" t="s">
+        <v>762</v>
+      </c>
+      <c r="D116" t="s">
+        <v>763</v>
+      </c>
+      <c r="E116" t="s">
+        <v>764</v>
+      </c>
+      <c r="F116" t="s">
+        <v>765</v>
+      </c>
+      <c r="G116" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>717</v>
+      </c>
+      <c r="B117" t="s">
+        <v>766</v>
+      </c>
+      <c r="C117" t="s">
+        <v>767</v>
+      </c>
+      <c r="D117" t="s">
+        <v>768</v>
+      </c>
+      <c r="E117" t="s">
+        <v>769</v>
+      </c>
+      <c r="F117" t="s">
+        <v>770</v>
+      </c>
+      <c r="G117" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>717</v>
+      </c>
+      <c r="B118" t="s">
+        <v>772</v>
+      </c>
+      <c r="C118" t="s">
+        <v>773</v>
+      </c>
+      <c r="D118" t="s">
+        <v>774</v>
+      </c>
+      <c r="E118" t="s">
+        <v>775</v>
+      </c>
+      <c r="F118" t="s">
+        <v>776</v>
+      </c>
+      <c r="G118" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>717</v>
+      </c>
+      <c r="B119" t="s">
+        <v>778</v>
+      </c>
+      <c r="C119" t="s">
+        <v>779</v>
+      </c>
+      <c r="D119" t="s">
+        <v>780</v>
+      </c>
+      <c r="E119" t="s">
+        <v>781</v>
+      </c>
+      <c r="F119" t="s">
+        <v>782</v>
+      </c>
+      <c r="G119" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>717</v>
+      </c>
+      <c r="B120" t="s">
+        <v>784</v>
+      </c>
+      <c r="C120" t="s">
+        <v>785</v>
+      </c>
+      <c r="D120" t="s">
+        <v>786</v>
+      </c>
+      <c r="E120" t="s">
+        <v>787</v>
+      </c>
+      <c r="F120" t="s">
+        <v>788</v>
+      </c>
+      <c r="G120" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>717</v>
+      </c>
+      <c r="B121" t="s">
+        <v>789</v>
+      </c>
+      <c r="C121" t="s">
+        <v>790</v>
+      </c>
+      <c r="D121" t="s">
+        <v>791</v>
+      </c>
+      <c r="E121" t="s">
+        <v>792</v>
+      </c>
+      <c r="F121" t="s">
+        <v>793</v>
+      </c>
+      <c r="G121" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>717</v>
+      </c>
+      <c r="B122" t="s">
+        <v>795</v>
+      </c>
+      <c r="C122" t="s">
+        <v>796</v>
+      </c>
+      <c r="D122" t="s">
+        <v>797</v>
+      </c>
+      <c r="E122" t="s">
+        <v>798</v>
+      </c>
+      <c r="F122" t="s">
+        <v>799</v>
+      </c>
+      <c r="G122" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>717</v>
+      </c>
+      <c r="B123" t="s">
+        <v>800</v>
+      </c>
+      <c r="C123" t="s">
+        <v>801</v>
+      </c>
+      <c r="D123" t="s">
+        <v>802</v>
+      </c>
+      <c r="E123" t="s">
+        <v>803</v>
+      </c>
+      <c r="F123" t="s">
+        <v>804</v>
+      </c>
+      <c r="G123" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>717</v>
+      </c>
+      <c r="B124" t="s">
+        <v>805</v>
+      </c>
+      <c r="C124" t="s">
+        <v>806</v>
+      </c>
+      <c r="D124" t="s">
+        <v>807</v>
+      </c>
+      <c r="E124" t="s">
+        <v>808</v>
+      </c>
+      <c r="F124" t="s">
+        <v>809</v>
+      </c>
+      <c r="G124" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>717</v>
+      </c>
+      <c r="B125" t="s">
+        <v>811</v>
+      </c>
+      <c r="C125" t="s">
+        <v>812</v>
+      </c>
+      <c r="D125" t="s">
+        <v>813</v>
+      </c>
+      <c r="E125" t="s">
+        <v>814</v>
+      </c>
+      <c r="F125" t="s">
+        <v>815</v>
+      </c>
+      <c r="G125" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>717</v>
+      </c>
+      <c r="B126" t="s">
+        <v>816</v>
+      </c>
+      <c r="C126" t="s">
+        <v>817</v>
+      </c>
+      <c r="D126" t="s">
+        <v>818</v>
+      </c>
+      <c r="E126" t="s">
+        <v>819</v>
+      </c>
+      <c r="F126" t="s">
+        <v>820</v>
+      </c>
+      <c r="G126" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>717</v>
+      </c>
+      <c r="B127" t="s">
+        <v>821</v>
+      </c>
+      <c r="C127" t="s">
+        <v>822</v>
+      </c>
+      <c r="D127" t="s">
+        <v>823</v>
+      </c>
+      <c r="E127" t="s">
+        <v>824</v>
+      </c>
+      <c r="F127" t="s">
+        <v>825</v>
+      </c>
+      <c r="G127" t="s">
         <v>76</v>
       </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>717</v>
+      </c>
+      <c r="B128" t="s">
+        <v>826</v>
+      </c>
+      <c r="C128" t="s">
+        <v>827</v>
+      </c>
+      <c r="D128" t="s">
+        <v>828</v>
+      </c>
+      <c r="E128" t="s">
+        <v>829</v>
+      </c>
+      <c r="F128" t="s">
+        <v>830</v>
+      </c>
+      <c r="G128" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>717</v>
+      </c>
+      <c r="B129" t="s">
+        <v>832</v>
+      </c>
+      <c r="C129" t="s">
+        <v>833</v>
+      </c>
+      <c r="D129" t="s">
+        <v>834</v>
+      </c>
+      <c r="E129" t="s">
+        <v>835</v>
+      </c>
+      <c r="F129" t="s">
+        <v>836</v>
+      </c>
+      <c r="G129" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>717</v>
+      </c>
+      <c r="B130" t="s">
+        <v>838</v>
+      </c>
+      <c r="C130" t="s">
+        <v>839</v>
+      </c>
+      <c r="D130" t="s">
+        <v>840</v>
+      </c>
+      <c r="E130" t="s">
+        <v>841</v>
+      </c>
+      <c r="F130" t="s">
+        <v>842</v>
+      </c>
+      <c r="G130" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>717</v>
+      </c>
+      <c r="B131" t="s">
+        <v>843</v>
+      </c>
+      <c r="C131" t="s">
+        <v>844</v>
+      </c>
+      <c r="D131" t="s">
+        <v>845</v>
+      </c>
+      <c r="E131" t="s">
+        <v>846</v>
+      </c>
+      <c r="F131" t="s">
+        <v>847</v>
+      </c>
+      <c r="G131" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>717</v>
+      </c>
+      <c r="B132" t="s">
+        <v>848</v>
+      </c>
+      <c r="C132" t="s">
+        <v>849</v>
+      </c>
+      <c r="D132" t="s">
+        <v>850</v>
+      </c>
+      <c r="E132" t="s">
+        <v>851</v>
+      </c>
+      <c r="F132" t="s">
+        <v>852</v>
+      </c>
+      <c r="G132" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>717</v>
+      </c>
+      <c r="B133" t="s">
+        <v>853</v>
+      </c>
+      <c r="C133" t="s">
+        <v>854</v>
+      </c>
+      <c r="D133" t="s">
+        <v>855</v>
+      </c>
+      <c r="E133" t="s">
+        <v>856</v>
+      </c>
+      <c r="F133" t="s">
+        <v>857</v>
+      </c>
+      <c r="G133" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>717</v>
+      </c>
+      <c r="B134" t="s">
+        <v>858</v>
+      </c>
+      <c r="C134" t="s">
+        <v>859</v>
+      </c>
+      <c r="D134" t="s">
+        <v>860</v>
+      </c>
+      <c r="E134" t="s">
+        <v>861</v>
+      </c>
+      <c r="F134" t="s">
+        <v>862</v>
+      </c>
+      <c r="G134" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>717</v>
+      </c>
+      <c r="B135" t="s">
+        <v>864</v>
+      </c>
+      <c r="C135" t="s">
+        <v>865</v>
+      </c>
+      <c r="D135" t="s">
+        <v>866</v>
+      </c>
+      <c r="E135" t="s">
+        <v>867</v>
+      </c>
+      <c r="F135" t="s">
+        <v>868</v>
+      </c>
+      <c r="G135" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>717</v>
+      </c>
+      <c r="B136" t="s">
+        <v>870</v>
+      </c>
+      <c r="C136" t="s">
+        <v>871</v>
+      </c>
+      <c r="D136" t="s">
+        <v>872</v>
+      </c>
+      <c r="E136" t="s">
+        <v>873</v>
+      </c>
+      <c r="F136" t="s">
+        <v>874</v>
+      </c>
+      <c r="G136" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>717</v>
+      </c>
+      <c r="B137" t="s">
+        <v>876</v>
+      </c>
+      <c r="C137" t="s">
+        <v>877</v>
+      </c>
+      <c r="D137" t="s">
+        <v>878</v>
+      </c>
+      <c r="E137" t="s">
+        <v>879</v>
+      </c>
+      <c r="F137" t="s">
+        <v>880</v>
+      </c>
+      <c r="G137" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>717</v>
+      </c>
+      <c r="B138" t="s">
+        <v>881</v>
+      </c>
+      <c r="C138" t="s">
+        <v>882</v>
+      </c>
+      <c r="D138" t="s">
+        <v>883</v>
+      </c>
+      <c r="E138" t="s">
+        <v>884</v>
+      </c>
+      <c r="F138" t="s">
+        <v>885</v>
+      </c>
+      <c r="G138" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>717</v>
+      </c>
+      <c r="B139" t="s">
+        <v>887</v>
+      </c>
+      <c r="C139" t="s">
+        <v>888</v>
+      </c>
+      <c r="D139" t="s">
+        <v>889</v>
+      </c>
+      <c r="E139" t="s">
+        <v>890</v>
+      </c>
+      <c r="F139" t="s">
+        <v>891</v>
+      </c>
+      <c r="G139" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>717</v>
+      </c>
+      <c r="B140" t="s">
+        <v>892</v>
+      </c>
+      <c r="C140" t="s">
+        <v>893</v>
+      </c>
+      <c r="D140" t="s">
+        <v>894</v>
+      </c>
+      <c r="E140" t="s">
+        <v>895</v>
+      </c>
+      <c r="F140" t="s">
+        <v>896</v>
+      </c>
+      <c r="G140" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>717</v>
+      </c>
+      <c r="B141" t="s">
+        <v>897</v>
+      </c>
+      <c r="C141" t="s">
+        <v>898</v>
+      </c>
+      <c r="D141" t="s">
+        <v>899</v>
+      </c>
+      <c r="E141" t="s">
+        <v>900</v>
+      </c>
+      <c r="F141" t="s">
+        <v>901</v>
+      </c>
+      <c r="G141" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>717</v>
+      </c>
+      <c r="B142" t="s">
+        <v>903</v>
+      </c>
+      <c r="C142" t="s">
+        <v>904</v>
+      </c>
+      <c r="D142" t="s">
+        <v>905</v>
+      </c>
+      <c r="E142" t="s">
+        <v>906</v>
+      </c>
+      <c r="F142" t="s">
+        <v>907</v>
+      </c>
+      <c r="G142" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>717</v>
+      </c>
+      <c r="B143" t="s">
+        <v>908</v>
+      </c>
+      <c r="C143" t="s">
+        <v>909</v>
+      </c>
+      <c r="D143" t="s">
+        <v>910</v>
+      </c>
+      <c r="E143" t="s">
+        <v>911</v>
+      </c>
+      <c r="F143" t="s">
+        <v>912</v>
+      </c>
+      <c r="G143" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>717</v>
+      </c>
+      <c r="B144" t="s">
+        <v>914</v>
+      </c>
+      <c r="C144" t="s">
+        <v>915</v>
+      </c>
+      <c r="D144" t="s">
+        <v>916</v>
+      </c>
+      <c r="E144" t="s">
+        <v>917</v>
+      </c>
+      <c r="F144" t="s">
+        <v>918</v>
+      </c>
+      <c r="G144" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>717</v>
+      </c>
+      <c r="B145" t="s">
+        <v>919</v>
+      </c>
+      <c r="C145" t="s">
+        <v>920</v>
+      </c>
+      <c r="D145" t="s">
+        <v>921</v>
+      </c>
+      <c r="E145" t="s">
+        <v>922</v>
+      </c>
+      <c r="F145" t="s">
+        <v>923</v>
+      </c>
+      <c r="G145" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>717</v>
+      </c>
+      <c r="B146" t="s">
+        <v>925</v>
+      </c>
+      <c r="C146" t="s">
+        <v>926</v>
+      </c>
+      <c r="D146" t="s">
+        <v>927</v>
+      </c>
+      <c r="E146" t="s">
+        <v>928</v>
+      </c>
+      <c r="F146" t="s">
+        <v>929</v>
+      </c>
+      <c r="G146" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>717</v>
+      </c>
+      <c r="B147" t="s">
+        <v>930</v>
+      </c>
+      <c r="C147" t="s">
+        <v>931</v>
+      </c>
+      <c r="D147" t="s">
+        <v>932</v>
+      </c>
+      <c r="E147" t="s">
+        <v>933</v>
+      </c>
+      <c r="F147" t="s">
+        <v>934</v>
+      </c>
+      <c r="G147" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>717</v>
+      </c>
+      <c r="B148" t="s">
+        <v>936</v>
+      </c>
+      <c r="C148" t="s">
+        <v>937</v>
+      </c>
+      <c r="D148" t="s">
+        <v>938</v>
+      </c>
+      <c r="E148" t="s">
+        <v>939</v>
+      </c>
+      <c r="F148" t="s">
+        <v>940</v>
+      </c>
+      <c r="G148" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>717</v>
+      </c>
+      <c r="B149" t="s">
+        <v>941</v>
+      </c>
+      <c r="C149" t="s">
+        <v>942</v>
+      </c>
+      <c r="D149" t="s">
+        <v>943</v>
+      </c>
+      <c r="E149" t="s">
+        <v>944</v>
+      </c>
+      <c r="F149" t="s">
+        <v>945</v>
+      </c>
+      <c r="G149" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>717</v>
+      </c>
+      <c r="B150" t="s">
+        <v>946</v>
+      </c>
+      <c r="C150" t="s">
+        <v>947</v>
+      </c>
+      <c r="D150" t="s">
+        <v>948</v>
+      </c>
+      <c r="E150" t="s">
+        <v>949</v>
+      </c>
+      <c r="F150" t="s">
+        <v>950</v>
+      </c>
+      <c r="G150" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>717</v>
+      </c>
+      <c r="B151" t="s">
+        <v>952</v>
+      </c>
+      <c r="C151" t="s">
+        <v>953</v>
+      </c>
+      <c r="D151" t="s">
+        <v>954</v>
+      </c>
+      <c r="E151" t="s">
+        <v>955</v>
+      </c>
+      <c r="F151" t="s">
+        <v>956</v>
+      </c>
+      <c r="G151" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>717</v>
+      </c>
+      <c r="B152" t="s">
+        <v>958</v>
+      </c>
+      <c r="C152" t="s">
+        <v>959</v>
+      </c>
+      <c r="D152" t="s">
+        <v>960</v>
+      </c>
+      <c r="E152" t="s">
+        <v>961</v>
+      </c>
+      <c r="F152" t="s">
+        <v>962</v>
+      </c>
+      <c r="G152" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>717</v>
+      </c>
+      <c r="B153" t="s">
+        <v>963</v>
+      </c>
+      <c r="C153" t="s">
+        <v>964</v>
+      </c>
+      <c r="D153" t="s">
+        <v>965</v>
+      </c>
+      <c r="E153" t="s">
+        <v>966</v>
+      </c>
+      <c r="F153" t="s">
+        <v>967</v>
+      </c>
+      <c r="G153" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>717</v>
+      </c>
+      <c r="B154" t="s">
+        <v>969</v>
+      </c>
+      <c r="C154" t="s">
+        <v>970</v>
+      </c>
+      <c r="D154" t="s">
+        <v>971</v>
+      </c>
+      <c r="E154" t="s">
+        <v>972</v>
+      </c>
+      <c r="F154" t="s">
+        <v>973</v>
+      </c>
+      <c r="G154" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>717</v>
+      </c>
+      <c r="B155" t="s">
+        <v>975</v>
+      </c>
+      <c r="C155" t="s">
+        <v>976</v>
+      </c>
+      <c r="D155" t="s">
+        <v>977</v>
+      </c>
+      <c r="E155" t="s">
+        <v>978</v>
+      </c>
+      <c r="F155" t="s">
+        <v>979</v>
+      </c>
+      <c r="G155" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>717</v>
+      </c>
+      <c r="B156" t="s">
+        <v>980</v>
+      </c>
+      <c r="C156" t="s">
+        <v>981</v>
+      </c>
+      <c r="D156" t="s">
+        <v>982</v>
+      </c>
+      <c r="E156" t="s">
+        <v>983</v>
+      </c>
+      <c r="F156" t="s">
+        <v>984</v>
+      </c>
+      <c r="G156" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>717</v>
+      </c>
+      <c r="B157" t="s">
+        <v>985</v>
+      </c>
+      <c r="C157" t="s">
+        <v>986</v>
+      </c>
+      <c r="D157" t="s">
+        <v>987</v>
+      </c>
+      <c r="E157" t="s">
+        <v>988</v>
+      </c>
+      <c r="F157" t="s">
+        <v>989</v>
+      </c>
+      <c r="G157" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>717</v>
+      </c>
+      <c r="B158" t="s">
+        <v>991</v>
+      </c>
+      <c r="C158" t="s">
+        <v>992</v>
+      </c>
+      <c r="D158" t="s">
+        <v>993</v>
+      </c>
+      <c r="E158" t="s">
+        <v>994</v>
+      </c>
+      <c r="F158" t="s">
+        <v>995</v>
+      </c>
+      <c r="G158" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>996</v>
+      </c>
+      <c r="B159" t="s">
+        <v>997</v>
+      </c>
+      <c r="C159" t="s">
+        <v>998</v>
+      </c>
+      <c r="D159" t="s">
+        <v>999</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G159" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>996</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E160" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G160" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>996</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G161" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>996</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G162" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>996</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E163" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G163" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>996</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E164" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G164" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>996</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E165" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G165" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>996</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E166" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G166" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>996</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E167" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G167" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>996</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G168" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>996</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E169" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G169" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E170" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G170" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G171" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G172" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G173" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G174" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E175" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G175" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G176" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G177" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G178" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G179" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G180" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G181" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G182" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G183" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G184" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G185" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F186" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G186" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G187" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G188" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G189" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G190" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G191" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="77.32875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="19.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="9.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>996</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>596</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F9" t="s">
+        <v>886</v>
       </c>
     </row>
   </sheetData>
